--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -626,7 +626,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/vaccine-gender</t>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -956,12 +959,6 @@
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
-  </si>
-  <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>NK1-15</t>
@@ -3372,9 +3369,11 @@
       <c r="X16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3407,16 +3406,16 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
@@ -3424,10 +3423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3450,19 +3449,19 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3511,7 +3510,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3526,27 +3525,27 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3569,19 +3568,19 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3630,7 +3629,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3645,7 +3644,7 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>169</v>
@@ -3654,7 +3653,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -3662,10 +3661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3688,19 +3687,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3749,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3764,16 +3763,16 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3781,10 +3780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3807,17 +3806,17 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3842,13 +3841,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3866,7 +3865,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3881,16 +3880,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -3898,10 +3897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3924,19 +3923,19 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3985,7 +3984,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4000,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>169</v>
@@ -4009,7 +4008,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4017,10 +4016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4043,19 +4042,19 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4104,7 +4103,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4119,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>169</v>
@@ -4128,7 +4127,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4136,10 +4135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4162,19 +4161,19 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4223,7 +4222,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4235,10 +4234,10 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>169</v>
@@ -4255,10 +4254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4281,13 +4280,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4338,7 +4337,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4370,10 +4369,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4399,10 +4398,10 @@
         <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>149</v>
@@ -4455,7 +4454,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4487,14 +4486,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4516,10 +4515,10 @@
         <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>149</v>
@@ -4574,7 +4573,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4606,10 +4605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4632,17 +4631,17 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4667,13 +4666,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4691,7 +4690,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4706,7 +4705,7 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>169</v>
@@ -4715,7 +4714,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4723,10 +4722,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4752,14 +4751,14 @@
         <v>172</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4808,7 +4807,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4832,7 +4831,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4840,10 +4839,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4869,13 +4868,13 @@
         <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>185</v>
@@ -4927,7 +4926,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4951,7 +4950,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4959,10 +4958,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4985,17 +4984,17 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5044,7 +5043,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5059,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>169</v>
@@ -5068,7 +5067,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5076,10 +5075,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5108,11 +5107,11 @@
         <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5140,10 +5139,10 @@
         <v>194</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>301</v>
+        <v>195</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>302</v>
+        <v>196</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5161,7 +5160,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5176,7 +5175,7 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>169</v>
@@ -5185,7 +5184,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5193,10 +5192,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5219,17 +5218,17 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5278,7 +5277,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5287,13 +5286,13 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>169</v>
@@ -5302,7 +5301,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5310,10 +5309,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5336,13 +5335,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5393,7 +5392,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5408,7 +5407,7 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>169</v>
@@ -5425,10 +5424,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5451,19 +5450,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5512,7 +5511,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5527,10 +5526,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5544,10 +5543,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5570,13 +5569,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5627,7 +5626,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5659,10 +5658,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5688,10 +5687,10 @@
         <v>133</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>149</v>
@@ -5744,7 +5743,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5776,14 +5775,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5805,10 +5804,10 @@
         <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>149</v>
@@ -5863,7 +5862,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5895,10 +5894,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5921,19 +5920,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5982,7 +5981,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -5997,16 +5996,16 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6014,10 +6013,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6043,16 +6042,16 @@
         <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6101,7 +6100,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6116,16 +6115,16 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6133,14 +6132,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6159,16 +6158,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6218,7 +6217,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6233,7 +6232,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>169</v>
@@ -6242,7 +6241,7 @@
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6250,10 +6249,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6276,19 +6275,19 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6337,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6352,10 +6351,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6369,10 +6368,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6395,19 +6394,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6456,7 +6455,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6471,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>169</v>
@@ -6488,10 +6487,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6514,13 +6513,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6571,7 +6570,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6603,10 +6602,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6632,10 +6631,10 @@
         <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>149</v>
@@ -6688,7 +6687,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6720,14 +6719,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6749,10 +6748,10 @@
         <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>149</v>
@@ -6807,7 +6806,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6839,10 +6838,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6865,16 +6864,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6924,7 +6923,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>88</v>
@@ -6948,7 +6947,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -6956,10 +6955,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6985,10 +6984,10 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7018,11 +7017,11 @@
         <v>194</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7039,7 +7038,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>88</v>
@@ -7054,7 +7053,7 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>169</v>

--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="368">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,21 +426,21 @@
     <t>Patient.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -450,28 +450,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Patient.extension:assessmentDate</t>
-  </si>
-  <si>
-    <t>assessmentDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/assessment-date}
-</t>
-  </si>
-  <si>
-    <t>The date on which the vaccination assessment was made.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Patient.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -479,9 +458,6 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -855,9 +831,6 @@
   </si>
   <si>
     <t>Patient.contact.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1492,12 +1465,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.48828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.48828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.4375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -1505,7 +1478,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.08203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.36328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2486,7 +2459,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2505,15 +2478,17 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2550,14 +2525,16 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2575,7 +2552,7 @@
         <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>20</v>
@@ -2595,41 +2572,43 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2677,7 +2656,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2686,13 +2665,13 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>20</v>
@@ -2716,7 +2695,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2729,13 +2708,13 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>147</v>
@@ -2743,11 +2722,9 @@
       <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2796,7 +2773,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2808,19 +2785,19 @@
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -2828,10 +2805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2842,84 +2819,88 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
@@ -2928,16 +2909,16 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -2945,10 +2926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2959,88 +2940,86 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -3049,16 +3028,16 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3066,10 +3045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3092,19 +3071,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3153,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3168,16 +3147,16 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3185,10 +3164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3199,7 +3178,7 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3211,19 +3190,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3248,13 +3227,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3272,13 +3251,13 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3287,16 +3266,16 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3304,10 +3283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3315,7 +3294,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>88</v>
@@ -3330,19 +3309,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3367,13 +3346,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3391,7 +3370,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3406,27 +3385,27 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3434,7 +3413,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3443,25 +3422,25 @@
         <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3510,7 +3489,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3525,27 +3504,27 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3556,31 +3535,31 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3629,13 +3608,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3644,16 +3623,16 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>169</v>
+        <v>218</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -3661,10 +3640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3675,7 +3654,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3684,22 +3663,20 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3724,13 +3701,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3748,13 +3725,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3763,16 +3740,16 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3780,10 +3757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3806,17 +3783,19 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3841,13 +3820,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3865,7 +3844,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3880,16 +3859,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -3897,10 +3876,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3911,7 +3890,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3923,19 +3902,19 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3984,13 +3963,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -3999,16 +3978,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4016,10 +3995,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4042,19 +4021,19 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4103,7 +4082,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4115,19 +4094,19 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>253</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4135,10 +4114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4149,7 +4128,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4161,20 +4140,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N23" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="O23" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4222,25 +4197,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4254,21 +4229,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4280,15 +4255,17 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4337,22 +4314,22 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -4369,14 +4346,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4389,24 +4366,26 @@
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4454,7 +4433,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4469,7 +4448,7 @@
         <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -4486,14 +4465,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4506,25 +4485,23 @@
         <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4549,13 +4526,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4573,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4585,19 +4562,19 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -4619,7 +4596,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4631,7 +4608,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>277</v>
@@ -4666,13 +4643,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4696,7 +4673,7 @@
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4705,16 +4682,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>282</v>
+        <v>170</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4722,10 +4699,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4736,7 +4713,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4748,17 +4725,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>178</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4807,13 +4786,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -4822,16 +4801,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4839,10 +4818,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4853,7 +4832,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4865,19 +4844,17 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>185</v>
+        <v>289</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4926,13 +4903,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -4941,16 +4918,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4958,10 +4935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4984,17 +4961,17 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>183</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5019,13 +4996,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5043,7 +5020,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5058,16 +5035,16 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5075,10 +5052,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5101,17 +5078,17 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5136,13 +5113,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5160,7 +5137,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5169,16 +5146,16 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5227,9 +5204,7 @@
         <v>306</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5286,22 +5261,22 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5309,10 +5284,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5323,7 +5298,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5335,16 +5310,20 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5392,13 +5371,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5407,10 +5386,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5424,10 +5403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5438,7 +5417,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5450,20 +5429,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5511,25 +5486,25 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5543,21 +5518,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5569,15 +5544,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5626,22 +5603,22 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -5658,14 +5635,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5678,24 +5655,26 @@
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5743,7 +5722,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5758,7 +5737,7 @@
         <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -5775,45 +5754,45 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>149</v>
+        <v>321</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>150</v>
+        <v>322</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5838,13 +5817,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5862,31 +5841,31 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>131</v>
+        <v>323</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5905,7 +5884,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -5920,7 +5899,7 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>327</v>
@@ -5957,13 +5936,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -5984,7 +5963,7 @@
         <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -6020,14 +5999,14 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6039,20 +6018,18 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6106,7 +6083,7 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6115,10 +6092,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>340</v>
+        <v>162</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6139,14 +6116,14 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6155,21 +6132,23 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6223,7 +6202,7 @@
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -6232,16 +6211,16 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6249,10 +6228,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6263,31 +6242,31 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6336,13 +6315,13 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6351,10 +6330,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6368,10 +6347,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6382,32 +6361,28 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>257</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6455,25 +6430,25 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>361</v>
+        <v>162</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6487,21 +6462,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6513,15 +6488,17 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6570,22 +6547,22 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
@@ -6602,14 +6579,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6622,24 +6599,26 @@
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6687,7 +6666,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6702,7 +6681,7 @@
         <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -6719,46 +6698,44 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>358</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>273</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>274</v>
+        <v>360</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6806,31 +6783,31 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -6838,10 +6815,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6864,17 +6841,15 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6899,13 +6874,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>365</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6923,7 +6898,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>88</v>
@@ -6938,133 +6913,18 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>157</v>
+        <v>367</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/cicada_ig/StructureDefinition-vax-patient.xlsx
+++ b/cicada_ig/StructureDefinition-vax-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
